--- a/Result/FormalGeo7KL6_Reports/MetricsTables.xlsx
+++ b/Result/FormalGeo7KL6_Reports/MetricsTables.xlsx
@@ -40,37 +40,37 @@
     <x:t>Inference Wall-Clock Time (s) - Solving</x:t>
   </x:si>
   <x:si>
-    <x:t>0.53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.93</x:t>
+    <x:t>0.57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.92</x:t>
   </x:si>
   <x:si>
     <x:t>Inference Wall-Clock Time (s) - Discovering</x:t>
   </x:si>
   <x:si>
-    <x:t>2.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.82</x:t>
+    <x:t>2.23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.15</x:t>
   </x:si>
   <x:si>
     <x:t>Peak Memory (MB) - Solving</x:t>
   </x:si>
   <x:si>
-    <x:t>138.66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1730.72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>254.09</x:t>
+    <x:t>138.44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1708.47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252.39</x:t>
   </x:si>
   <x:si>
     <x:t>Peak Memory (MB) - Discovering</x:t>
@@ -118,7 +118,7 @@
     <x:t>Count</x:t>
   </x:si>
   <x:si>
-    <x:t>34</x:t>
+    <x:t>33</x:t>
   </x:si>
   <x:si>
     <x:t>39</x:t>
@@ -130,7 +130,7 @@
     <x:t>Ratio</x:t>
   </x:si>
   <x:si>
-    <x:t>87.18%</x:t>
+    <x:t>84.62%</x:t>
   </x:si>
   <x:si>
     <x:t>100.00%</x:t>
@@ -376,10 +376,10 @@
     <x:t>97.50%</x:t>
   </x:si>
   <x:si>
-    <x:t>0.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.67</x:t>
+    <x:t>0.29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.19</x:t>
   </x:si>
   <x:si>
     <x:t>w/o Compass Matrix</x:t>
@@ -388,25 +388,25 @@
     <x:t>97.50% (0.0%)</x:t>
   </x:si>
   <x:si>
-    <x:t>0.65 (+22.3%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.36 (+32.7%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.29 (+22.3%)</x:t>
+    <x:t>0.72 (+26.1%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.41 (+43.8%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.00 (+26.1%)</x:t>
   </x:si>
   <x:si>
     <x:t>w/o Simplify Eq Sym</x:t>
   </x:si>
   <x:si>
-    <x:t>0.43 (-19.4%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.22 (-18.7%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.67 (-19.4%)</x:t>
+    <x:t>0.47 (-17.0%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.24 (-17.2%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.42 (-17.0%)</x:t>
   </x:si>
   <x:si>
     <x:t>Table 7: Top-5 Classic Semi Rule Pairs (Discovering)</x:t>
@@ -520,10 +520,10 @@
     <x:t>Matrix Sparsity</x:t>
   </x:si>
   <x:si>
-    <x:t>69.18%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.1314</x:t>
+    <x:t>69.26%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.1313</x:t>
   </x:si>
   <x:si>
     <x:t>QvQr Proportion</x:t>
@@ -544,31 +544,31 @@
     <x:t>0.0431</x:t>
   </x:si>
   <x:si>
-    <x:t>0.74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>149.89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2053.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>280.79</x:t>
+    <x:t>0.84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>150.22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1909.63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>280.21</x:t>
   </x:si>
   <x:si>
     <x:t>6231.49</x:t>
@@ -580,10 +580,10 @@
     <x:t>43666.00</x:t>
   </x:si>
   <x:si>
-    <x:t>31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79.49%</x:t>
+    <x:t>30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76.92%</x:t>
   </x:si>
   <x:si>
     <x:t>3595979</x:t>
@@ -709,28 +709,25 @@
     <x:t>49.25</x:t>
   </x:si>
   <x:si>
-    <x:t>0.38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.89 (+21.0%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.56 (+45.7%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34.88 (+21.0%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.51 (-30.9%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.37 (-3.5%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.93 (-30.9%)</x:t>
+    <x:t>32.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.98 (+16.7%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.61 (+32.6%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38.27 (+16.7%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.58 (-31.5%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.40 (-13.5%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.48 (-31.5%)</x:t>
   </x:si>
   <x:si>
     <x:t>17877439</x:t>
@@ -838,870 +835,873 @@
     <x:t>36.66</x:t>
   </x:si>
   <x:si>
-    <x:t>70.74%</x:t>
+    <x:t>70.72%</x:t>
   </x:si>
   <x:si>
     <x:t>0.1002</x:t>
   </x:si>
   <x:si>
+    <x:t>70.89%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57.44%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0220</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33.16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160.52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>921.55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>240.19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5400.05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44316985.07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36502.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69.23%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2795664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5490</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2046114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>718881</x:t>
+  </x:si>
+  <x:si>
+    <x:t>582</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99.92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>250120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99.81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1338628</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96.61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>447386</x:t>
+  </x:si>
+  <x:si>
+    <x:t>122952</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72.52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>292750</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81520</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72.15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>238687</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99.54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>130078</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83.76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2725</x:t>
+  </x:si>
+  <x:si>
+    <x:t>861</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>294</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78.01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>684</x:t>
+  </x:si>
+  <x:si>
+    <x:t>404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40.94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>633</x:t>
+  </x:si>
+  <x:si>
+    <x:t>231</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63.51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>370</x:t>
+  </x:si>
+  <x:si>
+    <x:t>181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51.08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41.40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.65 (+55.4%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.20 (+63.7%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64.33 (+55.4%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87.50% (-10.0%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.00 (-5.6%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.67 (-9.1%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35.06 (-15.3%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6969394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7642</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99.89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2861802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>521</x:t>
+  </x:si>
+  <x:si>
+    <x:t>783125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>428488</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1342396</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96.46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>450930</x:t>
+  </x:si>
+  <x:si>
+    <x:t>124300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72.43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>295590</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72.06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>239552</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1381</x:t>
+  </x:si>
+  <x:si>
+    <x:t>135586</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22996</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83.04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3314</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66.08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>699</x:t>
+  </x:si>
+  <x:si>
+    <x:t>264</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62.23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65.71%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.1065</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71.47%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62.14%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>213.84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91.76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>169.86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1177.94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>264.13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8612.70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>313005926.36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99226.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57.50%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91229982</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1220</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12878180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9909543</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14979</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6876256</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1255016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>275064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78.08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>776512</x:t>
+  </x:si>
+  <x:si>
+    <x:t>168672</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78.28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>504908</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57436</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88.62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>282072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35822</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87.30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>175273</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98.26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>864</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57.01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1358</x:t>
+  </x:si>
+  <x:si>
+    <x:t>333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75.48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>937</x:t>
+  </x:si>
+  <x:si>
+    <x:t>326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65.21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>432</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39.33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>359</x:t>
+  </x:si>
+  <x:si>
+    <x:t>192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46.52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56.18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100.00% (0.0%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.97 (+40.5%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.21 (+46.2%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78.95 (+40.5%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95.00% (-5.0%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.21 (-13.7%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.75 (-9.3%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46.06 (-18.0%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>514073438</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83352132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1276</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16205227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12440048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6891596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98.74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1641960</x:t>
+  </x:si>
+  <x:si>
+    <x:t>313496</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80.91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1031136</x:t>
+  </x:si>
+  <x:si>
+    <x:t>193984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81.19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>921769</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3069</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99.67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>501732</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43830</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91.26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62.93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69.73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64.69%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67.06%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61.64%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0234</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>195.10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73.60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>191.87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2363.07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>323.49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15416.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>267094204.06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74841.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.50%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92.50%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>646258285</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78289</x:t>
+  </x:si>
+  <x:si>
+    <x:t>414956690</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2721</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34421974</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34393648</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77701</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99.77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59822956</x:t>
+  </x:si>
+  <x:si>
+    <x:t>673504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98.87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32483233</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2795686</x:t>
+  </x:si>
+  <x:si>
+    <x:t>304912</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89.09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1857926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>206708</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88.87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1399638</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70830</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94.94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5875</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1792</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69.50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>491</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1589</x:t>
+  </x:si>
+  <x:si>
+    <x:t>443</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72.12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>701</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48.57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>532</x:t>
+  </x:si>
+  <x:si>
+    <x:t>236</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55.64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>141.27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.52 (+84.7%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.80 (+26.8%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>260.90 (+84.7%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90.00% (-10.0%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.97 (-15.8%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.88 (-15.0%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>107.08 (-24.2%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>124470483702</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5542827654</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5542799328</x:t>
+  </x:si>
+  <x:si>
+    <x:t>101612</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1479751170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2770</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68207836</x:t>
+  </x:si>
+  <x:si>
+    <x:t>929264</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98.64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42188265</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20570034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2098096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13513746</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1384088</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89.76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4930759</x:t>
+  </x:si>
+  <x:si>
+    <x:t>195324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96.04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9656</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75.91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>685</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80.84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74.58%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0596</x:t>
+  </x:si>
+  <x:si>
     <x:t>70.88%</x:t>
   </x:si>
   <x:si>
-    <x:t>0.0191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>57.44%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.0220</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>161.59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1097.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>240.64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5400.05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44316985.07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36502.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71.79%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2795664</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5490</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2046114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>471</x:t>
-  </x:si>
-  <x:si>
-    <x:t>718881</x:t>
-  </x:si>
-  <x:si>
-    <x:t>582</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99.92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>250120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99.81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1338628</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96.61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>447386</x:t>
-  </x:si>
-  <x:si>
-    <x:t>122952</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72.52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>292750</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81520</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>238687</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99.54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>130078</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21128</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83.76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2725</x:t>
-  </x:si>
-  <x:si>
-    <x:t>861</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>294</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>684</x:t>
-  </x:si>
-  <x:si>
-    <x:t>404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40.94</x:t>
-  </x:si>
-  <x:si>
-    <x:t>633</x:t>
-  </x:si>
-  <x:si>
-    <x:t>231</x:t>
-  </x:si>
-  <x:si>
-    <x:t>63.51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>370</x:t>
-  </x:si>
-  <x:si>
-    <x:t>181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>51.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.52 (+59.6%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.11 (+66.8%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>59.20 (+59.6%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87.50% (-10.0%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.89 (-6.8%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.58 (-12.8%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.01 (-16.4%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6969394</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7642</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99.89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2861802</x:t>
-  </x:si>
-  <x:si>
-    <x:t>521</x:t>
-  </x:si>
-  <x:si>
-    <x:t>783125</x:t>
-  </x:si>
-  <x:si>
-    <x:t>632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>428488</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1342396</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47516</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96.46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>450930</x:t>
-  </x:si>
-  <x:si>
-    <x:t>124300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72.43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>295590</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82596</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>239552</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1381</x:t>
-  </x:si>
-  <x:si>
-    <x:t>135586</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22996</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3314</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1124</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>699</x:t>
-  </x:si>
-  <x:si>
-    <x:t>264</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>65.61%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.1075</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71.45%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.0195</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62.14%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.0153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>207.69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90.43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>168.34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1278.79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>264.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8612.70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>313005926.36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99226.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62.50%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91229982</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1220</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12878180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1272</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9909543</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14979</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6876256</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1255016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>275064</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>776512</x:t>
-  </x:si>
-  <x:si>
-    <x:t>168672</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>504908</x:t>
-  </x:si>
-  <x:si>
-    <x:t>57436</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88.62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>282072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35822</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>175273</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>864</x:t>
-  </x:si>
-  <x:si>
-    <x:t>57.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1358</x:t>
-  </x:si>
-  <x:si>
-    <x:t>333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75.48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>937</x:t>
-  </x:si>
-  <x:si>
-    <x:t>326</x:t>
-  </x:si>
-  <x:si>
-    <x:t>65.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>432</x:t>
-  </x:si>
-  <x:si>
-    <x:t>39.33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>359</x:t>
-  </x:si>
-  <x:si>
-    <x:t>192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46.52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>51.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100.00% (0.0%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.79 (+40.1%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.10 (+49.9%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71.68 (+40.1%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95.00% (-5.0%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.12 (-12.6%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.68 (-6.9%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42.45 (-17.0%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>514073438</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1224</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83352132</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1276</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16205227</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23887</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12440048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6891596</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98.74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1641960</x:t>
-  </x:si>
-  <x:si>
-    <x:t>313496</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80.91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1031136</x:t>
-  </x:si>
-  <x:si>
-    <x:t>193984</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>921769</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3069</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99.67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>501732</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43830</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62.93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>69.73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>64.73%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.0970</x:t>
-  </x:si>
-  <x:si>
-    <x:t>67.06%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.0188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61.64%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.0234</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>180.66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73.48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>193.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2887.95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>343.48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15416.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>267094204.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74841.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.50%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95.00%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>646258285</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78289</x:t>
-  </x:si>
-  <x:si>
-    <x:t>414956690</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2721</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34421974</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34393648</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77701</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99.77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>59822956</x:t>
-  </x:si>
-  <x:si>
-    <x:t>673504</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98.87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32483233</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2795686</x:t>
-  </x:si>
-  <x:si>
-    <x:t>304912</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89.09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1857926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>206708</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88.87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1399638</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70830</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94.94</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5875</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1792</x:t>
-  </x:si>
-  <x:si>
-    <x:t>69.50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>491</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1589</x:t>
-  </x:si>
-  <x:si>
-    <x:t>443</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1363</x:t>
-  </x:si>
-  <x:si>
-    <x:t>701</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48.57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>532</x:t>
-  </x:si>
-  <x:si>
-    <x:t>236</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55.64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>128.17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.18 (+92.9%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.63 (+37.8%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>247.19 (+92.9%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90.00% (-10.0%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.66 (-16.9%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.65 (-13.5%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95.86 (-25.2%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>124470483702</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5542827654</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5542799328</x:t>
-  </x:si>
-  <x:si>
-    <x:t>101612</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1479751170</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2770</x:t>
-  </x:si>
-  <x:si>
-    <x:t>68207836</x:t>
-  </x:si>
-  <x:si>
-    <x:t>929264</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98.64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42188265</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13099</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20570034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2098096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13513746</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1384088</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89.76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4930759</x:t>
-  </x:si>
-  <x:si>
-    <x:t>195324</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9656</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2326</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75.91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>685</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80.84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74.57%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.0597</x:t>
-  </x:si>
-  <x:si>
     <x:t>0.0243</x:t>
   </x:si>
   <x:si>
@@ -1711,46 +1711,46 @@
     <x:t>0.0109</x:t>
   </x:si>
   <x:si>
-    <x:t>4.06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35.52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47.59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>336.57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>223.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>202.96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4355.60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>726.21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75117.56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>107203194517.93</x:t>
+    <x:t>4.58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44.69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54.19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>410.40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>248.88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>204.23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4893.35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>755.95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75221.47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>107201322623.12</x:t>
   </x:si>
   <x:si>
     <x:t>5077428.00</x:t>
   </x:si>
   <x:si>
-    <x:t>70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>263</x:t>
+    <x:t>62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>259</x:t>
   </x:si>
   <x:si>
     <x:t>284</x:t>
@@ -1759,25 +1759,25 @@
     <x:t>288</x:t>
   </x:si>
   <x:si>
-    <x:t>24.31%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91.32%</x:t>
+    <x:t>21.53%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89.93%</x:t>
   </x:si>
   <x:si>
     <x:t>98.61%</x:t>
   </x:si>
   <x:si>
-    <x:t>79317912926</x:t>
+    <x:t>79318423326</x:t>
   </x:si>
   <x:si>
     <x:t>17977</x:t>
   </x:si>
   <x:si>
-    <x:t>18854308332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>669372</x:t>
+    <x:t>19112490407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>673097</x:t>
   </x:si>
   <x:si>
     <x:t>6166190411</x:t>
@@ -1786,7 +1786,7 @@
     <x:t>18555</x:t>
   </x:si>
   <x:si>
-    <x:t>1905657814</x:t>
+    <x:t>1905934314</x:t>
   </x:si>
   <x:si>
     <x:t>4171287304</x:t>
@@ -1828,7 +1828,7 @@
     <x:t>98.41</x:t>
   </x:si>
   <x:si>
-    <x:t>88719</x:t>
+    <x:t>88721</x:t>
   </x:si>
   <x:si>
     <x:t>17578</x:t>
@@ -1876,46 +1876,46 @@
     <x:t>98.29%</x:t>
   </x:si>
   <x:si>
-    <x:t>2.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1170.63</x:t>
+    <x:t>2.44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1318.14</x:t>
   </x:si>
   <x:si>
     <x:t>98.29% (0.0%)</x:t>
   </x:si>
   <x:si>
-    <x:t>9.41 (+131.5%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.68 (+68.4%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2710.33 (+131.5%)</x:t>
+    <x:t>11.72 (+156.0%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.98 (+63.1%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3374.60 (+156.0%)</x:t>
   </x:si>
   <x:si>
     <x:t>93.17% (-5.1%)</x:t>
   </x:si>
   <x:si>
-    <x:t>3.28 (-19.3%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.63 (-25.3%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>895.26 (-23.5%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>109337401217</x:t>
+    <x:t>3.71 (-19.0%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.82 (-25.3%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1012.61 (-23.2%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>109338283217</x:t>
   </x:si>
   <x:si>
     <x:t>18244</x:t>
   </x:si>
   <x:si>
-    <x:t>36824421426</x:t>
-  </x:si>
-  <x:si>
-    <x:t>894738</x:t>
+    <x:t>36823538551</x:t>
+  </x:si>
+  <x:si>
+    <x:t>894613</x:t>
   </x:si>
   <x:si>
     <x:t>7106986845</x:t>
@@ -1924,7 +1924,7 @@
     <x:t>18677</x:t>
   </x:si>
   <x:si>
-    <x:t>2951409587</x:t>
+    <x:t>2951546087</x:t>
   </x:si>
   <x:si>
     <x:t>4171893512</x:t>
@@ -1987,19 +1987,19 @@
     <x:t>AngleSin</x:t>
   </x:si>
   <x:si>
-    <x:t>4924</x:t>
+    <x:t>4923</x:t>
   </x:si>
   <x:si>
     <x:t>2564</x:t>
   </x:si>
   <x:si>
-    <x:t>47.93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77.88%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.0590</x:t>
+    <x:t>47.92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77.79%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.0593</x:t>
   </x:si>
   <x:si>
     <x:t>75.83%</x:t>
@@ -2041,19 +2041,19 @@
     <x:t>Inference Wall-Clock Time (s)</x:t>
   </x:si>
   <x:si>
-    <x:t>2.96</x:t>
+    <x:t>3.32</x:t>
   </x:si>
   <x:si>
     <x:t>Peak Memory (MB)</x:t>
   </x:si>
   <x:si>
-    <x:t>186.53</x:t>
+    <x:t>187.23</x:t>
   </x:si>
   <x:si>
     <x:t>Actual Rule Instantiations</x:t>
   </x:si>
   <x:si>
-    <x:t>47706.71</x:t>
+    <x:t>47768.42</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2517,13 +2517,13 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>470</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
         <x:v>563</x:v>
@@ -2543,13 +2543,13 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>380</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>476</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
         <x:v>569</x:v>
@@ -2569,13 +2569,13 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>287</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>383</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>479</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
         <x:v>572</x:v>
@@ -4195,10 +4195,10 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="D44" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E44" s="3" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="E44" s="3" t="s">
-        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
@@ -4209,13 +4209,13 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="C45" s="3" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D45" s="3" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="D45" s="3" t="s">
+      <x:c r="E45" s="3" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="E45" s="3" t="s">
-        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
@@ -4226,13 +4226,13 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="C46" s="4" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D46" s="4" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="D46" s="4" t="s">
+      <x:c r="E46" s="4" t="s">
         <x:v>235</x:v>
-      </x:c>
-      <x:c r="E46" s="4" t="s">
-        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -4269,13 +4269,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C51" s="3" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D51" s="3" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="D51" s="3" t="s">
+      <x:c r="E51" s="3" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="E51" s="3" t="s">
-        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -4286,13 +4286,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C52" s="3" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D52" s="3" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="D52" s="3" t="s">
+      <x:c r="E52" s="3" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="E52" s="3" t="s">
-        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -4303,13 +4303,13 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="C53" s="3" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D53" s="3" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="D53" s="3" t="s">
+      <x:c r="E53" s="3" t="s">
         <x:v>241</x:v>
-      </x:c>
-      <x:c r="E53" s="3" t="s">
-        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
@@ -4320,10 +4320,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C54" s="3" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="D54" s="3" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E54" s="3" t="s">
         <x:v>132</x:v>
@@ -4337,13 +4337,13 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C55" s="4" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D55" s="4" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="D55" s="4" t="s">
+      <x:c r="E55" s="4" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="E55" s="4" t="s">
-        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6">
@@ -4380,13 +4380,13 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C58" s="3" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D58" s="3" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D58" s="3" t="s">
+      <x:c r="E58" s="3" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="E58" s="3" t="s">
-        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -4397,13 +4397,13 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C59" s="3" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D59" s="3" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D59" s="3" t="s">
+      <x:c r="E59" s="3" t="s">
         <x:v>251</x:v>
-      </x:c>
-      <x:c r="E59" s="3" t="s">
-        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
@@ -4414,13 +4414,13 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C60" s="3" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D60" s="3" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="D60" s="3" t="s">
+      <x:c r="E60" s="3" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="E60" s="3" t="s">
-        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -4431,13 +4431,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C61" s="3" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D61" s="3" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="D61" s="3" t="s">
+      <x:c r="E61" s="3" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="E61" s="3" t="s">
-        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
@@ -4448,13 +4448,13 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="C62" s="4" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D62" s="4" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="D62" s="4" t="s">
+      <x:c r="E62" s="4" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="E62" s="4" t="s">
-        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -4491,13 +4491,13 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C65" s="3" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D65" s="3" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="D65" s="3" t="s">
+      <x:c r="E65" s="3" t="s">
         <x:v>263</x:v>
-      </x:c>
-      <x:c r="E65" s="3" t="s">
-        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
@@ -4525,13 +4525,13 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C67" s="3" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D67" s="3" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="D67" s="3" t="s">
+      <x:c r="E67" s="3" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="E67" s="3" t="s">
-        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
@@ -4556,16 +4556,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B69" s="4" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="C69" s="4" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="C69" s="4" t="s">
+      <x:c r="D69" s="4" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="D69" s="4" t="s">
+      <x:c r="E69" s="4" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="E69" s="4" t="s">
-        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6">
@@ -4591,10 +4591,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B74" s="3" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="s">
-        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
@@ -4602,10 +4602,10 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B75" s="3" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="C75" s="3" t="s">
         <x:v>274</x:v>
-      </x:c>
-      <x:c r="C75" s="3" t="s">
-        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6">
@@ -4613,10 +4613,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B76" s="4" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="C76" s="4" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="C76" s="4" t="s">
-        <x:v>277</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4684,13 +4684,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
+      <x:c r="D3" s="3" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -4698,13 +4698,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="D4" s="3" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="D4" s="3" t="s">
-        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -4712,13 +4712,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="s">
+      <x:c r="D5" s="3" t="s">
         <x:v>285</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="s">
-        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -4740,13 +4740,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="s">
+      <x:c r="D7" s="3" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="D7" s="3" t="s">
-        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -4806,7 +4806,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>290</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
         <x:v>33</x:v>
@@ -4826,7 +4826,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
         <x:v>37</x:v>
@@ -4875,13 +4875,13 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="D21" s="3" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="D21" s="3" t="s">
+      <x:c r="E21" s="3" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="E21" s="3" t="s">
-        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -4892,10 +4892,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="D22" s="3" t="s">
         <x:v>295</x:v>
-      </x:c>
-      <x:c r="D22" s="3" t="s">
-        <x:v>296</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
         <x:v>132</x:v>
@@ -4909,10 +4909,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="s">
         <x:v>295</x:v>
-      </x:c>
-      <x:c r="D23" s="3" t="s">
-        <x:v>296</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
         <x:v>132</x:v>
@@ -4926,13 +4926,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="D24" s="3" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="D24" s="3" t="s">
+      <x:c r="E24" s="3" t="s">
         <x:v>298</x:v>
-      </x:c>
-      <x:c r="E24" s="3" t="s">
-        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -4943,13 +4943,13 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="s">
         <x:v>300</x:v>
-      </x:c>
-      <x:c r="D25" s="4" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="E25" s="4" t="s">
-        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -4986,13 +4986,13 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="D28" s="3" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="D28" s="3" t="s">
+      <x:c r="E28" s="3" t="s">
         <x:v>303</x:v>
-      </x:c>
-      <x:c r="E28" s="3" t="s">
-        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -5003,13 +5003,13 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="D29" s="3" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="D29" s="3" t="s">
+      <x:c r="E29" s="3" t="s">
         <x:v>306</x:v>
-      </x:c>
-      <x:c r="E29" s="3" t="s">
-        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -5020,13 +5020,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="D30" s="3" t="s">
+      <x:c r="E30" s="3" t="s">
         <x:v>309</x:v>
-      </x:c>
-      <x:c r="E30" s="3" t="s">
-        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -5037,13 +5037,13 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="D31" s="3" t="s">
+      <x:c r="E31" s="3" t="s">
         <x:v>312</x:v>
-      </x:c>
-      <x:c r="E31" s="3" t="s">
-        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
@@ -5054,13 +5054,13 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C32" s="4" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D32" s="4" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="D32" s="4" t="s">
+      <x:c r="E32" s="4" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="E32" s="4" t="s">
-        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
@@ -5097,10 +5097,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="D35" s="3" t="s">
         <x:v>317</x:v>
-      </x:c>
-      <x:c r="D35" s="3" t="s">
-        <x:v>318</x:v>
       </x:c>
       <x:c r="E35" s="3" t="s">
         <x:v>223</x:v>
@@ -5114,13 +5114,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="D36" s="3" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="D36" s="3" t="s">
+      <x:c r="E36" s="3" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="E36" s="3" t="s">
-        <x:v>321</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
@@ -5131,13 +5131,13 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="D37" s="3" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="D37" s="3" t="s">
+      <x:c r="E37" s="3" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="E37" s="3" t="s">
-        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -5148,13 +5148,13 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="D38" s="3" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="D38" s="3" t="s">
+      <x:c r="E38" s="3" t="s">
         <x:v>326</x:v>
-      </x:c>
-      <x:c r="E38" s="3" t="s">
-        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
@@ -5165,13 +5165,13 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="C39" s="4" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="D39" s="4" t="s">
+      <x:c r="E39" s="4" t="s">
         <x:v>329</x:v>
-      </x:c>
-      <x:c r="E39" s="4" t="s">
-        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
@@ -5208,13 +5208,13 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="C44" s="3" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D44" s="3" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="E44" s="3" t="s">
         <x:v>331</x:v>
-      </x:c>
-      <x:c r="E44" s="3" t="s">
-        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
@@ -5225,13 +5225,13 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="C45" s="3" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="D45" s="3" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="D45" s="3" t="s">
+      <x:c r="E45" s="3" t="s">
         <x:v>334</x:v>
-      </x:c>
-      <x:c r="E45" s="3" t="s">
-        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
@@ -5239,16 +5239,16 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B46" s="4" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="C46" s="4" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="C46" s="4" t="s">
+      <x:c r="D46" s="4" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="D46" s="4" t="s">
+      <x:c r="E46" s="4" t="s">
         <x:v>338</x:v>
-      </x:c>
-      <x:c r="E46" s="4" t="s">
-        <x:v>339</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -5285,13 +5285,13 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="C51" s="3" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="D51" s="3" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="D51" s="3" t="s">
+      <x:c r="E51" s="3" t="s">
         <x:v>341</x:v>
-      </x:c>
-      <x:c r="E51" s="3" t="s">
-        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -5302,10 +5302,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C52" s="3" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="D52" s="3" t="s">
         <x:v>343</x:v>
-      </x:c>
-      <x:c r="D52" s="3" t="s">
-        <x:v>344</x:v>
       </x:c>
       <x:c r="E52" s="3" t="s">
         <x:v>132</x:v>
@@ -5319,10 +5319,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C53" s="3" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="D53" s="3" t="s">
         <x:v>343</x:v>
-      </x:c>
-      <x:c r="D53" s="3" t="s">
-        <x:v>344</x:v>
       </x:c>
       <x:c r="E53" s="3" t="s">
         <x:v>132</x:v>
@@ -5336,13 +5336,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C54" s="3" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="D54" s="3" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="D54" s="3" t="s">
-        <x:v>346</x:v>
-      </x:c>
       <x:c r="E54" s="3" t="s">
-        <x:v>299</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
@@ -5353,10 +5353,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C55" s="4" t="s">
-        <x:v>347</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="D55" s="4" t="s">
-        <x:v>344</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="E55" s="4" t="s">
         <x:v>134</x:v>
@@ -5396,13 +5396,13 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C58" s="3" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="D58" s="3" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="D58" s="3" t="s">
+      <x:c r="E58" s="3" t="s">
         <x:v>349</x:v>
-      </x:c>
-      <x:c r="E58" s="3" t="s">
-        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -5413,13 +5413,13 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C59" s="3" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="D59" s="3" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="D59" s="3" t="s">
+      <x:c r="E59" s="3" t="s">
         <x:v>352</x:v>
-      </x:c>
-      <x:c r="E59" s="3" t="s">
-        <x:v>353</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
@@ -5430,13 +5430,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C60" s="3" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="D60" s="3" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="D60" s="3" t="s">
+      <x:c r="E60" s="3" t="s">
         <x:v>355</x:v>
-      </x:c>
-      <x:c r="E60" s="3" t="s">
-        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -5447,10 +5447,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C61" s="3" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="D61" s="3" t="s">
         <x:v>357</x:v>
-      </x:c>
-      <x:c r="D61" s="3" t="s">
-        <x:v>358</x:v>
       </x:c>
       <x:c r="E61" s="3" t="s">
         <x:v>202</x:v>
@@ -5464,13 +5464,13 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C62" s="4" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="D62" s="4" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="D62" s="4" t="s">
+      <x:c r="E62" s="4" t="s">
         <x:v>360</x:v>
-      </x:c>
-      <x:c r="E62" s="4" t="s">
-        <x:v>361</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -5507,13 +5507,13 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C65" s="3" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D65" s="3" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="D65" s="3" t="s">
+      <x:c r="E65" s="3" t="s">
         <x:v>363</x:v>
-      </x:c>
-      <x:c r="E65" s="3" t="s">
-        <x:v>364</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
@@ -5524,13 +5524,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C66" s="3" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="D66" s="3" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="D66" s="3" t="s">
+      <x:c r="E66" s="3" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="E66" s="3" t="s">
-        <x:v>321</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
@@ -5541,13 +5541,13 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C67" s="3" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="D67" s="3" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="D67" s="3" t="s">
+      <x:c r="E67" s="3" t="s">
         <x:v>366</x:v>
-      </x:c>
-      <x:c r="E67" s="3" t="s">
-        <x:v>367</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
@@ -5558,13 +5558,13 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C68" s="3" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="D68" s="3" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="D68" s="3" t="s">
+      <x:c r="E68" s="3" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="E68" s="3" t="s">
-        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:6">
@@ -5575,13 +5575,13 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="C69" s="4" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="D69" s="4" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="D69" s="4" t="s">
+      <x:c r="E69" s="4" t="s">
         <x:v>329</x:v>
-      </x:c>
-      <x:c r="E69" s="4" t="s">
-        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6">
@@ -5607,10 +5607,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B74" s="3" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="s">
         <x:v>368</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="s">
-        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
@@ -5618,10 +5618,10 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B75" s="3" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="C75" s="3" t="s">
         <x:v>370</x:v>
-      </x:c>
-      <x:c r="C75" s="3" t="s">
-        <x:v>371</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6">
@@ -5629,10 +5629,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B76" s="4" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="C76" s="4" t="s">
         <x:v>372</x:v>
-      </x:c>
-      <x:c r="C76" s="4" t="s">
-        <x:v>373</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5700,13 +5700,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
+      <x:c r="D3" s="3" t="s">
         <x:v>375</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>376</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -5714,13 +5714,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="D4" s="3" t="s">
         <x:v>378</x:v>
-      </x:c>
-      <x:c r="D4" s="3" t="s">
-        <x:v>379</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -5728,13 +5728,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="s">
+      <x:c r="D5" s="3" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="s">
-        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -5756,13 +5756,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="s">
+      <x:c r="D7" s="3" t="s">
         <x:v>384</x:v>
-      </x:c>
-      <x:c r="D7" s="3" t="s">
-        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -5822,16 +5822,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="C15" s="3" t="s">
-        <x:v>387</x:v>
-      </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>387</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>387</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>34</x:v>
@@ -5842,7 +5842,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>388</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
         <x:v>37</x:v>
@@ -5891,13 +5891,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="D21" s="3" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="D21" s="3" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -5908,13 +5908,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="D22" s="3" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="D22" s="3" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
@@ -5925,10 +5925,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="s">
         <x:v>391</x:v>
-      </x:c>
-      <x:c r="D23" s="3" t="s">
-        <x:v>392</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
         <x:v>190</x:v>
@@ -5942,13 +5942,13 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="D24" s="3" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="D24" s="3" t="s">
-        <x:v>394</x:v>
-      </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -5959,10 +5959,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
-        <x:v>395</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>390</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E25" s="4" t="s">
         <x:v>132</x:v>
@@ -6002,13 +6002,13 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="D28" s="3" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="D28" s="3" t="s">
+      <x:c r="E28" s="3" t="s">
         <x:v>397</x:v>
-      </x:c>
-      <x:c r="E28" s="3" t="s">
-        <x:v>398</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -6019,13 +6019,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="D29" s="3" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="D29" s="3" t="s">
+      <x:c r="E29" s="3" t="s">
         <x:v>400</x:v>
-      </x:c>
-      <x:c r="E29" s="3" t="s">
-        <x:v>401</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -6036,13 +6036,13 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="s">
         <x:v>402</x:v>
       </x:c>
-      <x:c r="D30" s="3" t="s">
+      <x:c r="E30" s="3" t="s">
         <x:v>403</x:v>
-      </x:c>
-      <x:c r="E30" s="3" t="s">
-        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -6053,13 +6053,13 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="s">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="D31" s="3" t="s">
+      <x:c r="E31" s="3" t="s">
         <x:v>406</x:v>
-      </x:c>
-      <x:c r="E31" s="3" t="s">
-        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
@@ -6070,13 +6070,13 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C32" s="4" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="D32" s="4" t="s">
         <x:v>408</x:v>
       </x:c>
-      <x:c r="D32" s="4" t="s">
+      <x:c r="E32" s="4" t="s">
         <x:v>409</x:v>
-      </x:c>
-      <x:c r="E32" s="4" t="s">
-        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
@@ -6113,13 +6113,13 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="D35" s="3" t="s">
         <x:v>411</x:v>
       </x:c>
-      <x:c r="D35" s="3" t="s">
+      <x:c r="E35" s="3" t="s">
         <x:v>412</x:v>
-      </x:c>
-      <x:c r="E35" s="3" t="s">
-        <x:v>413</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
@@ -6130,13 +6130,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="D36" s="3" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="D36" s="3" t="s">
+      <x:c r="E36" s="3" t="s">
         <x:v>415</x:v>
-      </x:c>
-      <x:c r="E36" s="3" t="s">
-        <x:v>416</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
@@ -6147,13 +6147,13 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="D37" s="3" t="s">
         <x:v>417</x:v>
       </x:c>
-      <x:c r="D37" s="3" t="s">
+      <x:c r="E37" s="3" t="s">
         <x:v>418</x:v>
-      </x:c>
-      <x:c r="E37" s="3" t="s">
-        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -6164,13 +6164,13 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="D38" s="3" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="D38" s="3" t="s">
+      <x:c r="E38" s="3" t="s">
         <x:v>421</x:v>
-      </x:c>
-      <x:c r="E38" s="3" t="s">
-        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
@@ -6181,13 +6181,13 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="C39" s="4" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="D39" s="4" t="s">
+      <x:c r="E39" s="4" t="s">
         <x:v>424</x:v>
-      </x:c>
-      <x:c r="E39" s="4" t="s">
-        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
@@ -6224,13 +6224,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C44" s="3" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="D44" s="3" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="E44" s="3" t="s">
         <x:v>426</x:v>
-      </x:c>
-      <x:c r="E44" s="3" t="s">
-        <x:v>427</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
@@ -6238,16 +6238,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B45" s="3" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="C45" s="3" t="s">
         <x:v>428</x:v>
       </x:c>
-      <x:c r="C45" s="3" t="s">
+      <x:c r="D45" s="3" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="D45" s="3" t="s">
+      <x:c r="E45" s="3" t="s">
         <x:v>430</x:v>
-      </x:c>
-      <x:c r="E45" s="3" t="s">
-        <x:v>431</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
@@ -6255,16 +6255,16 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B46" s="4" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="C46" s="4" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="C46" s="4" t="s">
+      <x:c r="D46" s="4" t="s">
         <x:v>433</x:v>
       </x:c>
-      <x:c r="D46" s="4" t="s">
+      <x:c r="E46" s="4" t="s">
         <x:v>434</x:v>
-      </x:c>
-      <x:c r="E46" s="4" t="s">
-        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -6301,13 +6301,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C51" s="3" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="D51" s="3" t="s">
         <x:v>436</x:v>
       </x:c>
-      <x:c r="D51" s="3" t="s">
-        <x:v>437</x:v>
-      </x:c>
       <x:c r="E51" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -6318,13 +6318,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C52" s="3" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="D52" s="3" t="s">
         <x:v>436</x:v>
       </x:c>
-      <x:c r="D52" s="3" t="s">
-        <x:v>437</x:v>
-      </x:c>
       <x:c r="E52" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -6335,13 +6335,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C53" s="3" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="D53" s="3" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="D53" s="3" t="s">
-        <x:v>439</x:v>
-      </x:c>
       <x:c r="E53" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
@@ -6352,13 +6352,13 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="C54" s="3" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="D54" s="3" t="s">
         <x:v>440</x:v>
       </x:c>
-      <x:c r="D54" s="3" t="s">
-        <x:v>441</x:v>
-      </x:c>
       <x:c r="E54" s="3" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
@@ -6369,10 +6369,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C55" s="4" t="s">
-        <x:v>442</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D55" s="4" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="E55" s="4" t="s">
         <x:v>190</x:v>
@@ -6412,13 +6412,13 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C58" s="3" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="D58" s="3" t="s">
         <x:v>443</x:v>
       </x:c>
-      <x:c r="D58" s="3" t="s">
+      <x:c r="E58" s="3" t="s">
         <x:v>444</x:v>
-      </x:c>
-      <x:c r="E58" s="3" t="s">
-        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -6429,13 +6429,13 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C59" s="3" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="D59" s="3" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="D59" s="3" t="s">
+      <x:c r="E59" s="3" t="s">
         <x:v>447</x:v>
-      </x:c>
-      <x:c r="E59" s="3" t="s">
-        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
@@ -6446,13 +6446,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C60" s="3" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="D60" s="3" t="s">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="D60" s="3" t="s">
+      <x:c r="E60" s="3" t="s">
         <x:v>450</x:v>
-      </x:c>
-      <x:c r="E60" s="3" t="s">
-        <x:v>451</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -6463,13 +6463,13 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C61" s="3" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="D61" s="3" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="D61" s="3" t="s">
+      <x:c r="E61" s="3" t="s">
         <x:v>453</x:v>
-      </x:c>
-      <x:c r="E61" s="3" t="s">
-        <x:v>454</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
@@ -6480,13 +6480,13 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C62" s="4" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="D62" s="4" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="D62" s="4" t="s">
+      <x:c r="E62" s="4" t="s">
         <x:v>456</x:v>
-      </x:c>
-      <x:c r="E62" s="4" t="s">
-        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -6523,13 +6523,13 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C65" s="3" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="D65" s="3" t="s">
         <x:v>458</x:v>
       </x:c>
-      <x:c r="D65" s="3" t="s">
+      <x:c r="E65" s="3" t="s">
         <x:v>459</x:v>
-      </x:c>
-      <x:c r="E65" s="3" t="s">
-        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
@@ -6540,13 +6540,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C66" s="3" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="D66" s="3" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="D66" s="3" t="s">
+      <x:c r="E66" s="3" t="s">
         <x:v>415</x:v>
-      </x:c>
-      <x:c r="E66" s="3" t="s">
-        <x:v>416</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
@@ -6557,13 +6557,13 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C67" s="3" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="D67" s="3" t="s">
         <x:v>461</x:v>
       </x:c>
-      <x:c r="D67" s="3" t="s">
+      <x:c r="E67" s="3" t="s">
         <x:v>462</x:v>
-      </x:c>
-      <x:c r="E67" s="3" t="s">
-        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
@@ -6574,13 +6574,13 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C68" s="3" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="D68" s="3" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="D68" s="3" t="s">
+      <x:c r="E68" s="3" t="s">
         <x:v>421</x:v>
-      </x:c>
-      <x:c r="E68" s="3" t="s">
-        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:6">
@@ -6591,13 +6591,13 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="C69" s="4" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D69" s="4" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="D69" s="4" t="s">
+      <x:c r="E69" s="4" t="s">
         <x:v>424</x:v>
-      </x:c>
-      <x:c r="E69" s="4" t="s">
-        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6">
@@ -6623,10 +6623,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B74" s="3" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="s">
         <x:v>464</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="s">
-        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
@@ -6634,10 +6634,10 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B75" s="3" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="C75" s="3" t="s">
         <x:v>466</x:v>
-      </x:c>
-      <x:c r="C75" s="3" t="s">
-        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6">
@@ -6645,10 +6645,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B76" s="4" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="C76" s="4" t="s">
         <x:v>468</x:v>
-      </x:c>
-      <x:c r="C76" s="4" t="s">
-        <x:v>469</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6716,13 +6716,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
         <x:v>470</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
+      <x:c r="D3" s="3" t="s">
         <x:v>471</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -6730,13 +6730,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
         <x:v>473</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="D4" s="3" t="s">
         <x:v>474</x:v>
-      </x:c>
-      <x:c r="D4" s="3" t="s">
-        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -6744,13 +6744,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="s">
+      <x:c r="D5" s="3" t="s">
         <x:v>477</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="s">
-        <x:v>478</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -6772,13 +6772,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
         <x:v>479</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="s">
+      <x:c r="D7" s="3" t="s">
         <x:v>480</x:v>
-      </x:c>
-      <x:c r="D7" s="3" t="s">
-        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -6838,16 +6838,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="s">
         <x:v>482</x:v>
       </x:c>
-      <x:c r="C15" s="3" t="s">
-        <x:v>483</x:v>
-      </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>387</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>387</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
         <x:v>34</x:v>
@@ -6858,10 +6858,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="s">
         <x:v>484</x:v>
-      </x:c>
-      <x:c r="C16" s="4" t="s">
-        <x:v>485</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
         <x:v>37</x:v>
@@ -6907,10 +6907,10 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="D21" s="3" t="s">
         <x:v>486</x:v>
-      </x:c>
-      <x:c r="D21" s="3" t="s">
-        <x:v>487</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
         <x:v>190</x:v>
@@ -6924,13 +6924,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="3" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="D22" s="3" t="s">
         <x:v>488</x:v>
       </x:c>
-      <x:c r="D22" s="3" t="s">
-        <x:v>489</x:v>
-      </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
@@ -6941,13 +6941,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="s">
         <x:v>488</x:v>
       </x:c>
-      <x:c r="D23" s="3" t="s">
-        <x:v>489</x:v>
-      </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -6958,10 +6958,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D24" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
         <x:v>190</x:v>
@@ -6975,13 +6975,13 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="s">
         <x:v>491</x:v>
       </x:c>
-      <x:c r="D25" s="4" t="s">
+      <x:c r="E25" s="4" t="s">
         <x:v>492</x:v>
-      </x:c>
-      <x:c r="E25" s="4" t="s">
-        <x:v>493</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -7018,13 +7018,13 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C28" s="3" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="D28" s="3" t="s">
         <x:v>494</x:v>
       </x:c>
-      <x:c r="D28" s="3" t="s">
+      <x:c r="E28" s="3" t="s">
         <x:v>495</x:v>
-      </x:c>
-      <x:c r="E28" s="3" t="s">
-        <x:v>496</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -7035,10 +7035,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="D29" s="3" t="s">
         <x:v>497</x:v>
-      </x:c>
-      <x:c r="D29" s="3" t="s">
-        <x:v>498</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
         <x:v>49</x:v>
@@ -7052,13 +7052,13 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="s">
         <x:v>499</x:v>
       </x:c>
-      <x:c r="D30" s="3" t="s">
+      <x:c r="E30" s="3" t="s">
         <x:v>500</x:v>
-      </x:c>
-      <x:c r="E30" s="3" t="s">
-        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -7069,13 +7069,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="s">
         <x:v>502</x:v>
       </x:c>
-      <x:c r="D31" s="3" t="s">
+      <x:c r="E31" s="3" t="s">
         <x:v>503</x:v>
-      </x:c>
-      <x:c r="E31" s="3" t="s">
-        <x:v>504</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
@@ -7086,13 +7086,13 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="C32" s="4" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="D32" s="4" t="s">
         <x:v>505</x:v>
       </x:c>
-      <x:c r="D32" s="4" t="s">
+      <x:c r="E32" s="4" t="s">
         <x:v>506</x:v>
-      </x:c>
-      <x:c r="E32" s="4" t="s">
-        <x:v>507</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
@@ -7129,13 +7129,13 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="D35" s="3" t="s">
         <x:v>508</x:v>
       </x:c>
-      <x:c r="D35" s="3" t="s">
+      <x:c r="E35" s="3" t="s">
         <x:v>509</x:v>
-      </x:c>
-      <x:c r="E35" s="3" t="s">
-        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
@@ -7146,13 +7146,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="D36" s="3" t="s">
         <x:v>511</x:v>
       </x:c>
-      <x:c r="D36" s="3" t="s">
+      <x:c r="E36" s="3" t="s">
         <x:v>512</x:v>
-      </x:c>
-      <x:c r="E36" s="3" t="s">
-        <x:v>513</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
@@ -7163,13 +7163,13 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="D37" s="3" t="s">
         <x:v>514</x:v>
       </x:c>
-      <x:c r="D37" s="3" t="s">
+      <x:c r="E37" s="3" t="s">
         <x:v>515</x:v>
-      </x:c>
-      <x:c r="E37" s="3" t="s">
-        <x:v>516</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -7180,13 +7180,13 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="D38" s="3" t="s">
         <x:v>517</x:v>
       </x:c>
-      <x:c r="D38" s="3" t="s">
+      <x:c r="E38" s="3" t="s">
         <x:v>518</x:v>
-      </x:c>
-      <x:c r="E38" s="3" t="s">
-        <x:v>519</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
@@ -7197,13 +7197,13 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="C39" s="4" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="D39" s="4" t="s">
+      <x:c r="E39" s="4" t="s">
         <x:v>521</x:v>
-      </x:c>
-      <x:c r="E39" s="4" t="s">
-        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
@@ -7240,13 +7240,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C44" s="3" t="s">
-        <x:v>470</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="D44" s="3" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="E44" s="3" t="s">
         <x:v>523</x:v>
-      </x:c>
-      <x:c r="E44" s="3" t="s">
-        <x:v>524</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
@@ -7254,16 +7254,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B45" s="3" t="s">
-        <x:v>428</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C45" s="3" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="D45" s="3" t="s">
         <x:v>525</x:v>
       </x:c>
-      <x:c r="D45" s="3" t="s">
+      <x:c r="E45" s="3" t="s">
         <x:v>526</x:v>
-      </x:c>
-      <x:c r="E45" s="3" t="s">
-        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
@@ -7271,16 +7271,16 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B46" s="4" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="C46" s="4" t="s">
         <x:v>528</x:v>
       </x:c>
-      <x:c r="C46" s="4" t="s">
+      <x:c r="D46" s="4" t="s">
         <x:v>529</x:v>
       </x:c>
-      <x:c r="D46" s="4" t="s">
+      <x:c r="E46" s="4" t="s">
         <x:v>530</x:v>
-      </x:c>
-      <x:c r="E46" s="4" t="s">
-        <x:v>531</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -7317,13 +7317,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C51" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D51" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E51" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -7334,13 +7334,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C52" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="D52" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E52" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -7351,13 +7351,13 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C53" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="D53" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E53" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
@@ -7368,13 +7368,13 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C54" s="3" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="D54" s="3" t="s">
         <x:v>534</x:v>
       </x:c>
-      <x:c r="D54" s="3" t="s">
-        <x:v>535</x:v>
-      </x:c>
       <x:c r="E54" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
@@ -7385,13 +7385,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C55" s="4" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="D55" s="4" t="s">
         <x:v>536</x:v>
       </x:c>
-      <x:c r="D55" s="4" t="s">
-        <x:v>537</x:v>
-      </x:c>
       <x:c r="E55" s="4" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6">
@@ -7428,13 +7428,13 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C58" s="3" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="D58" s="3" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D58" s="3" t="s">
+      <x:c r="E58" s="3" t="s">
         <x:v>539</x:v>
-      </x:c>
-      <x:c r="E58" s="3" t="s">
-        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -7445,10 +7445,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C59" s="3" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="D59" s="3" t="s">
         <x:v>541</x:v>
-      </x:c>
-      <x:c r="D59" s="3" t="s">
-        <x:v>542</x:v>
       </x:c>
       <x:c r="E59" s="3" t="s">
         <x:v>49</x:v>
@@ -7462,13 +7462,13 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C60" s="3" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="D60" s="3" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="D60" s="3" t="s">
+      <x:c r="E60" s="3" t="s">
         <x:v>544</x:v>
-      </x:c>
-      <x:c r="E60" s="3" t="s">
-        <x:v>545</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -7479,13 +7479,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C61" s="3" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="D61" s="3" t="s">
         <x:v>546</x:v>
       </x:c>
-      <x:c r="D61" s="3" t="s">
+      <x:c r="E61" s="3" t="s">
         <x:v>547</x:v>
-      </x:c>
-      <x:c r="E61" s="3" t="s">
-        <x:v>548</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
@@ -7496,13 +7496,13 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C62" s="4" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="D62" s="4" t="s">
         <x:v>549</x:v>
       </x:c>
-      <x:c r="D62" s="4" t="s">
+      <x:c r="E62" s="4" t="s">
         <x:v>550</x:v>
-      </x:c>
-      <x:c r="E62" s="4" t="s">
-        <x:v>551</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -7539,13 +7539,13 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C65" s="3" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="D65" s="3" t="s">
         <x:v>552</x:v>
       </x:c>
-      <x:c r="D65" s="3" t="s">
+      <x:c r="E65" s="3" t="s">
         <x:v>553</x:v>
-      </x:c>
-      <x:c r="E65" s="3" t="s">
-        <x:v>554</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
@@ -7556,13 +7556,13 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C66" s="3" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="D66" s="3" t="s">
         <x:v>555</x:v>
       </x:c>
-      <x:c r="D66" s="3" t="s">
+      <x:c r="E66" s="3" t="s">
         <x:v>556</x:v>
-      </x:c>
-      <x:c r="E66" s="3" t="s">
-        <x:v>557</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
@@ -7573,13 +7573,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C67" s="3" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="D67" s="3" t="s">
         <x:v>511</x:v>
       </x:c>
-      <x:c r="D67" s="3" t="s">
+      <x:c r="E67" s="3" t="s">
         <x:v>512</x:v>
-      </x:c>
-      <x:c r="E67" s="3" t="s">
-        <x:v>513</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
@@ -7590,13 +7590,13 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C68" s="3" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="D68" s="3" t="s">
         <x:v>517</x:v>
       </x:c>
-      <x:c r="D68" s="3" t="s">
+      <x:c r="E68" s="3" t="s">
         <x:v>518</x:v>
-      </x:c>
-      <x:c r="E68" s="3" t="s">
-        <x:v>519</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:6">
@@ -7607,13 +7607,13 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="C69" s="4" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="D69" s="4" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="D69" s="4" t="s">
+      <x:c r="E69" s="4" t="s">
         <x:v>521</x:v>
-      </x:c>
-      <x:c r="E69" s="4" t="s">
-        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6">
@@ -7639,10 +7639,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B74" s="3" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="s">
         <x:v>558</x:v>
-      </x:c>
-      <x:c r="C74" s="3" t="s">
-        <x:v>559</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
@@ -7650,7 +7650,7 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B75" s="3" t="s">
-        <x:v>274</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="C75" s="3" t="s">
         <x:v>560</x:v>
@@ -7929,7 +7929,7 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -7946,7 +7946,7 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
@@ -7963,7 +7963,7 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -7980,7 +7980,7 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="E24" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -7997,7 +7997,7 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="E25" s="4" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -8040,7 +8040,7 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="E28" s="3" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -8210,7 +8210,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B39" s="4" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C39" s="4" t="s">
         <x:v>614</x:v>
@@ -8339,7 +8339,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="E51" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -8356,7 +8356,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="E52" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -8373,7 +8373,7 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="E53" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
@@ -8390,7 +8390,7 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="E54" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
@@ -8407,7 +8407,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="E55" s="4" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6">
@@ -8450,7 +8450,7 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="E58" s="3" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
